--- a/public/samples/absences_demo.xlsx
+++ b/public/samples/absences_demo.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,9 +436,6 @@
       <c r="L1" t="str">
         <v>Tel</v>
       </c>
-      <c r="M1" t="str">
-        <v>__dup</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -1164,10 +1161,10 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Clinique Saint-Amand</v>
+        <v>Ateliers Mécaniques du Nord</v>
       </c>
       <c r="B21" t="str">
-        <v>44219876500027</v>
+        <v>39847503200014</v>
       </c>
       <c r="C21" t="str">
         <v>Dubois</v>
@@ -1199,13 +1196,10 @@
       <c r="L21" t="str">
         <v/>
       </c>
-      <c r="M21" t="str">
-        <v>doublon fichier</v>
-      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>